--- a/данные/тест_реал/заполненные/Учителя - Четверг.xlsx
+++ b/данные/тест_реал/заполненные/Учителя - Четверг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LuMon1x\AMSUR\данные\тест_реал\заполненные\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C656F76-CFDB-481C-A352-E3D57910E518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A72C2E1-B524-4D72-83AF-423808A94FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="104">
   <si>
     <t>Преподователи</t>
   </si>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t>к/ч:6а</t>
+  </si>
+  <si>
+    <t>к/ч:5в</t>
   </si>
 </sst>
 </file>
@@ -1556,7 +1559,7 @@
         <v>97</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
